--- a/artfynd/A 857-2024 artfynd.xlsx
+++ b/artfynd/A 857-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2532,6 +2532,228 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120135690</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kuuravaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>865203</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7411883</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk, Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120136766</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91832</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kuuravaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>865186</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7411902</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk, Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 857-2024 artfynd.xlsx
+++ b/artfynd/A 857-2024 artfynd.xlsx
@@ -2537,7 +2537,7 @@
         <v>120135690</v>
       </c>
       <c r="B18" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>120136766</v>
       </c>
       <c r="B19" t="n">
-        <v>91832</v>
+        <v>91850</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 857-2024 artfynd.xlsx
+++ b/artfynd/A 857-2024 artfynd.xlsx
@@ -2643,7 +2643,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 857-2024 artfynd.xlsx
+++ b/artfynd/A 857-2024 artfynd.xlsx
@@ -2534,10 +2534,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120135690</v>
+        <v>120136766</v>
       </c>
       <c r="B18" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2546,25 +2546,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>865203</v>
+        <v>865186</v>
       </c>
       <c r="R18" t="n">
-        <v>7411883</v>
+        <v>7411902</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2610,19 +2610,9 @@
           <t>2024-09-13</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>16:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2643,17 +2633,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120136766</v>
+        <v>120135690</v>
       </c>
       <c r="B19" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2662,25 +2652,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2693,10 +2683,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>865186</v>
+        <v>865203</v>
       </c>
       <c r="R19" t="n">
-        <v>7411902</v>
+        <v>7411883</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2726,9 +2716,19 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
